--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>item name</t>
   </si>
@@ -59,6 +59,24 @@
   </si>
   <si>
     <t>https://www.aliexpress.us/item/2251832827320422.html?src=google&amp;pdp_npi=4%40dis%21USD%2113.26%2112.76%21%21%21%21%21%40%2167063291251%21ppc%21%21%21&amp;gatewayAdapt=glo2usa</t>
+  </si>
+  <si>
+    <t>Aluminum Extrusions</t>
+  </si>
+  <si>
+    <t>3D Printed Parts</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Lengths (mm)</t>
+  </si>
+  <si>
+    <t>Coner Brackets:</t>
+  </si>
+  <si>
+    <t>Width</t>
   </si>
 </sst>
 </file>
@@ -71,13 +89,19 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -418,12 +442,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -544,139 +583,145 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -989,15 +1034,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelRow="5" outlineLevelCol="3"/>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13.5045045045045" customWidth="1"/>
     <col min="2" max="2" width="73.054054054054" customWidth="1"/>
     <col min="4" max="4" width="189.738738738739" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4">
+    <row r="1" spans="1:6">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1008,7 +1053,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="2:4">
+    <row r="2" spans="1:6">
       <c r="B2" t="s">
         <v>3</v>
       </c>
@@ -1016,7 +1061,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:4">
+    <row r="3" spans="1:6">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -1024,7 +1069,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:4">
+    <row r="4" spans="1:6">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -1032,7 +1077,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:4">
+    <row r="5" spans="1:6">
       <c r="B5" t="s">
         <v>7</v>
       </c>
@@ -1040,13 +1085,152 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:4">
+    <row r="6" spans="1:6">
       <c r="B6" t="s">
         <v>8</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>
       </c>
+    </row>
+    <row r="9" ht="14.85"/>
+    <row r="10" ht="25.6" spans="1:6">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" ht="25.6" spans="1:6">
+      <c r="A11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" ht="14.85" spans="1:6">
+      <c r="A12" s="2">
+        <v>500</v>
+      </c>
+      <c r="B12" s="2">
+        <v>13</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" ht="14.85" spans="1:6">
+      <c r="A13" s="2">
+        <v>1700</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" ht="14.85" spans="1:6">
+      <c r="A14" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B14" s="2">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" ht="14.85" spans="1:6">
+      <c r="A15" s="2">
+        <v>600</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" ht="14.85" spans="1:6">
+      <c r="A16" s="2">
+        <v>850</v>
+      </c>
+      <c r="B16" s="2">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" ht="14.85" spans="1:6">
+      <c r="A17" s="2">
+        <v>350</v>
+      </c>
+      <c r="B17" s="2">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" ht="14.85" spans="1:6">
+      <c r="A18" s="2">
+        <v>450</v>
+      </c>
+      <c r="B18" s="2">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" ht="14.85" spans="1:6">
+      <c r="A19" s="2">
+        <v>250</v>
+      </c>
+      <c r="B19" s="2">
+        <v>6</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" ht="14.85" spans="1:6">
+      <c r="A20" s="2">
+        <v>200</v>
+      </c>
+      <c r="B20" s="2">
+        <v>2</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
